--- a/submission/HAS-FY2026.xlsx
+++ b/submission/HAS-FY2026.xlsx
@@ -577,7 +577,7 @@
         <x:v>GBPm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>900</x:v>
+        <x:v>890</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -588,7 +588,7 @@
         <x:v>GBp</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>1.5</x:v>
+        <x:v>1.21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -599,7 +599,7 @@
         <x:v>GBPm</x:v>
       </x:c>
       <x:c r="C9" s="34">
-        <x:v>45</x:v>
+        <x:v>44.9</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/HAS-FY2026.xlsx
+++ b/submission/HAS-FY2026.xlsx
@@ -577,7 +577,7 @@
         <x:v>GBPm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>890</x:v>
+        <x:v>897</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -588,7 +588,7 @@
         <x:v>GBp</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>1.21</x:v>
+        <x:v>1.2</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -599,7 +599,7 @@
         <x:v>GBPm</x:v>
       </x:c>
       <x:c r="C9" s="34">
-        <x:v>44.9</x:v>
+        <x:v>45.2</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/HAS-FY2026.xlsx
+++ b/submission/HAS-FY2026.xlsx
@@ -588,7 +588,7 @@
         <x:v>GBp</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>1.2</x:v>
+        <x:v>1.275</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">

--- a/submission/HAS-FY2026.xlsx
+++ b/submission/HAS-FY2026.xlsx
@@ -577,7 +577,7 @@
         <x:v>GBPm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>897</x:v>
+        <x:v>896</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -588,7 +588,7 @@
         <x:v>GBp</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>1.275</x:v>
+        <x:v>1.25</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">

--- a/submission/HAS-FY2026.xlsx
+++ b/submission/HAS-FY2026.xlsx
@@ -577,7 +577,7 @@
         <x:v>GBPm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>896</x:v>
+        <x:v>897.5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -588,7 +588,7 @@
         <x:v>GBp</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>1.25</x:v>
+        <x:v>1.3</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
